--- a/xls/ab_tree.xlsx
+++ b/xls/ab_tree.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868"/>
   </bookViews>
   <sheets>
     <sheet name="normal" sheetId="1" r:id="rId1"/>
     <sheet name="test" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>"type":"skill",
 "id":"fireball",
@@ -78,6 +79,16 @@
     <t>"type":"skill",
 "id":"heal",
 "x":125,"y":25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"type":"link",
+"pts":[
+{"x":75,"y":75},
+{"x":75,"y":100}],
+"refs":[
+"lunge",
+"fireball"]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -457,7 +468,7 @@
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="3"/>
     </row>
     <row r="2" spans="1:4" ht="113.4">
       <c r="A2" s="1" t="s">
@@ -484,7 +495,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -503,6 +514,58 @@
         <v>6</v>
       </c>
     </row>
+    <row r="2" spans="1:3">
+      <c r="B2" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
+  <cols>
+    <col min="1" max="1" width="24.5546875" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="19.88671875" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="97.2">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="113.4">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" ht="48.6">
+      <c r="A3" s="2"/>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/xls/ab_tree.xlsx
+++ b/xls/ab_tree.xlsx
@@ -4,91 +4,157 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868"/>
+    <workbookView xWindow="264" yWindow="228" windowWidth="19200" windowHeight="7980" activeTab="7"/>
   </bookViews>
   <sheets>
-    <sheet name="normal" sheetId="1" r:id="rId1"/>
-    <sheet name="test" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="geneeral" sheetId="1" r:id="rId1"/>
+    <sheet name="sword" sheetId="2" r:id="rId2"/>
+    <sheet name="archery" sheetId="3" r:id="rId3"/>
+    <sheet name="fire" sheetId="4" r:id="rId4"/>
+    <sheet name="ice" sheetId="5" r:id="rId5"/>
+    <sheet name="poison" sheetId="6" r:id="rId6"/>
+    <sheet name="support" sheetId="7" r:id="rId7"/>
+    <sheet name="enhancement" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
-  <si>
-    <t>"type":"skill",
-"id":"fireball",
-"x":125,"y":25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"type":"skill",
-"id":"lunge",
-"x":25,"y":25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"type":"link",
-"pts":[
-{"x":25,"y":50},
-{"x":25,"y":75},
-{"x":75,"y":75}],
-"refs":["lunge"]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"type":"link",
-"pts":[
-{"x":125,"y":50},
-{"x":125,"y":75},
-{"x":75,"y":75}],
-"refs":["fireball"]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"type":"skill",
-"id":"strong",
-"x":25,"y":25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"type":"link",
-"pts":[
-{"x":75,"y":75},
-{"x":75,"y":100}],
-"refs":[
-"lunge",
-"fireball"]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"type":"skill",
-"id":"test1",
-"x":225,"y":25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"type":"skill",
-"id":"ice",
-"x":75,"y":125</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"type":"skill",
-"id":"heal",
-"x":125,"y":25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"type":"link",
-"pts":[
-{"x":75,"y":75},
-{"x":75,"y":100}],
-"refs":[
-"lunge",
-"fireball"]</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+  <si>
+    <t>"id":"stealing",
+"x":1,"y":1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"lockpicking",
+"x":3,"y":1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"skinning",
+"x":5,"y":1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"stealth",
+"x":1,"y":3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"barter",
+"x":3,"y":3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"slash",
+"x":1,"y":1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"thrust",
+"x":3,"y":1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"whirlwind",
+"x":2,"y":3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"snipe",
+"x":1,"y":1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"fireball",
+"x":1,"y":1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"firewall",
+"x":3,"y":1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"combustion",
+"x":2,"y":3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"meteorshower",
+"x":2,"y":5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"icebolt",
+"x":1,"y":1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"icewall",
+"x":3,"y":1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"deepfreeze",
+"x":2,"y":3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"blizzard",
+"x":2,"y":5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"poisondart",
+"x":1,"y":1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"poisonmist",
+"x":3,"y":1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"venomburst",
+"x":2,"y":3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"heal",
+"x":1,"y":1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"cure",
+"x":3,"y":1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"holylight",
+"x":5,"y":1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"purify",
+"x":4,"y":3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"strboost",
+"x":1,"y":1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"agiboost",
+"x":3,"y":1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"id":"intboost",
+"x":5,"y":1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -96,7 +162,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -119,6 +185,13 @@
       <family val="1"/>
       <charset val="136"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體 Light"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -143,7 +216,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -155,6 +228,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -450,41 +529,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="16.44140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="24.21875" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="9.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.21875" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="48.6">
+    <row r="1" spans="1:6" ht="32.4">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3"/>
-    </row>
-    <row r="2" spans="1:4" ht="113.4">
-      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" spans="1:6" ht="35.4" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" ht="32.4">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="48.6">
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -495,27 +581,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.5546875" customWidth="1"/>
     <col min="2" max="2" width="17.77734375" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="48.6">
+    <row r="1" spans="1:3" ht="32.4">
       <c r="A1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>8</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B1" s="3"/>
       <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="B2" s="1"/>
+    <row r="2" spans="1:3" ht="38.4" customHeight="1">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" ht="32.4">
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -528,43 +619,249 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="24.5546875" customWidth="1"/>
+    <col min="1" max="1" width="18.109375" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="19.88671875" customWidth="1"/>
     <col min="4" max="4" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="97.2">
+    <row r="1" spans="1:4" ht="32.4">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="113.4">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" ht="48.6">
+    <row r="3" spans="1:4">
       <c r="A3" s="2"/>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="B3" s="1"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="17.6640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="23" style="5" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="31.2">
+      <c r="A1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="40.799999999999997" customHeight="1">
+      <c r="A2" s="4"/>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" spans="1:3" ht="31.2">
+      <c r="B3" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36" customHeight="1">
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:3" ht="31.2">
+      <c r="B5" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="17.44140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="22" style="5" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="31.2">
+      <c r="A1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="40.200000000000003" customHeight="1">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" spans="1:3" ht="31.2">
+      <c r="B3" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36" customHeight="1">
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:3" ht="31.2">
+      <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="21" style="5" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="31.2">
+      <c r="A1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="46.8" customHeight="1">
+      <c r="A2" s="4"/>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" spans="1:3" ht="31.2">
+      <c r="B3" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="B5" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="21" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="23.88671875" style="5" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="31.2">
+      <c r="A1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="43.2" customHeight="1">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="31.2">
+      <c r="B3" s="4"/>
+      <c r="D3" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="17.88671875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.21875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="5"/>
+    <col min="5" max="5" width="18.77734375" style="5" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="31.2">
+      <c r="A1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/xls/ab_tree.xlsx
+++ b/xls/ab_tree.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="264" yWindow="228" windowWidth="19200" windowHeight="7980" activeTab="7"/>
   </bookViews>
   <sheets>
-    <sheet name="geneeral" sheetId="1" r:id="rId1"/>
-    <sheet name="sword" sheetId="2" r:id="rId2"/>
-    <sheet name="archery" sheetId="3" r:id="rId3"/>
-    <sheet name="fire" sheetId="4" r:id="rId4"/>
-    <sheet name="ice" sheetId="5" r:id="rId5"/>
-    <sheet name="poison" sheetId="6" r:id="rId6"/>
-    <sheet name="support" sheetId="7" r:id="rId7"/>
-    <sheet name="enhancement" sheetId="8" r:id="rId8"/>
+    <sheet name="General" sheetId="1" r:id="rId1"/>
+    <sheet name="Sword" sheetId="2" r:id="rId2"/>
+    <sheet name="Archery" sheetId="3" r:id="rId3"/>
+    <sheet name="Fire" sheetId="4" r:id="rId4"/>
+    <sheet name="Ice" sheetId="5" r:id="rId5"/>
+    <sheet name="Poison" sheetId="6" r:id="rId6"/>
+    <sheet name="Support" sheetId="7" r:id="rId7"/>
+    <sheet name="Enhancement" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -23,138 +23,111 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
-    <t>"id":"stealing",
-"x":1,"y":1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"lockpicking",
-"x":3,"y":1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"skinning",
-"x":5,"y":1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"stealth",
-"x":1,"y":3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"barter",
-"x":3,"y":3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"slash",
-"x":1,"y":1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"thrust",
-"x":3,"y":1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"whirlwind",
-"x":2,"y":3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"snipe",
-"x":1,"y":1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"fireball",
-"x":1,"y":1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"firewall",
-"x":3,"y":1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"combustion",
-"x":2,"y":3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"meteorshower",
-"x":2,"y":5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"icebolt",
-"x":1,"y":1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"icewall",
-"x":3,"y":1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"deepfreeze",
-"x":2,"y":3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"blizzard",
-"x":2,"y":5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"poisondart",
-"x":1,"y":1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"poisonmist",
-"x":3,"y":1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"venomburst",
-"x":2,"y":3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"heal",
-"x":1,"y":1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"cure",
-"x":3,"y":1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"holylight",
-"x":5,"y":1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"purify",
-"x":4,"y":3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"strboost",
-"x":1,"y":1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"agiboost",
-"x":3,"y":1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"id":"intboost",
-"x":5,"y":1</t>
+    <t>stealing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stealth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lockpicking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>barter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skinning</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>whirlwind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thrust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snipe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fireball</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>combustion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meteorshower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>firewall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icebolt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icewall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deepfreeze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blizzard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poisondart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>venomburst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poisonmist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>holylight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>purify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strboost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agiboost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intboost</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -532,26 +505,26 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="9.88671875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="2" customWidth="1"/>
     <col min="4" max="4" width="11.21875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="24.21875" style="2" customWidth="1"/>
     <col min="7" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.4">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" s="3"/>
     </row>
@@ -562,13 +535,13 @@
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:6" ht="32.4">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -584,18 +557,18 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="15.5546875" customWidth="1"/>
-    <col min="2" max="2" width="17.77734375" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" customWidth="1"/>
     <col min="3" max="3" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="32.4">
+    <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="38.4" customHeight="1">
@@ -603,9 +576,9 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:3" ht="32.4">
+    <row r="3" spans="1:3">
       <c r="B3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -619,13 +592,13 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="19.88671875" customWidth="1"/>
     <col min="4" max="4" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="32.4">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -656,35 +629,35 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="23" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11.88671875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="17" style="5" customWidth="1"/>
     <col min="3" max="3" width="18.33203125" style="5" customWidth="1"/>
     <col min="4" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="31.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="40.799999999999997" customHeight="1">
       <c r="A2" s="4"/>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" spans="1:3" ht="31.2">
+    <row r="3" spans="1:3">
       <c r="B3" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="36" customHeight="1">
       <c r="B4" s="4"/>
     </row>
-    <row r="5" spans="1:3" ht="31.2">
+    <row r="5" spans="1:3">
       <c r="B5" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -698,13 +671,13 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="22" style="5" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" style="5" customWidth="1"/>
     <col min="3" max="3" width="18.33203125" style="5" customWidth="1"/>
     <col min="4" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="31.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
         <v>13</v>
       </c>
@@ -717,7 +690,7 @@
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" spans="1:3" ht="31.2">
+    <row r="3" spans="1:3">
       <c r="B3" s="4" t="s">
         <v>15</v>
       </c>
@@ -725,7 +698,7 @@
     <row r="4" spans="1:3" ht="36" customHeight="1">
       <c r="B4" s="4"/>
     </row>
-    <row r="5" spans="1:3" ht="31.2">
+    <row r="5" spans="1:3">
       <c r="B5" s="4" t="s">
         <v>16</v>
       </c>
@@ -741,27 +714,27 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="21" style="5" customWidth="1"/>
-    <col min="2" max="2" width="21.88671875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" style="5" customWidth="1"/>
     <col min="3" max="3" width="21.5546875" style="5" customWidth="1"/>
     <col min="4" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="31.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="46.8" customHeight="1">
       <c r="A2" s="4"/>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" spans="1:3" ht="31.2">
+    <row r="3" spans="1:3">
       <c r="B3" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -781,15 +754,15 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="21" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11" style="5" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="23.88671875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="13" style="5" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="31.2">
+    <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>20</v>
       </c>
@@ -807,7 +780,7 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:5" ht="31.2">
+    <row r="3" spans="1:5">
       <c r="B3" s="4"/>
       <c r="D3" s="4" t="s">
         <v>23</v>
@@ -830,15 +803,15 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="17.88671875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" style="5" customWidth="1"/>
     <col min="2" max="2" width="11.21875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="16.5546875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="5" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="5"/>
-    <col min="5" max="5" width="18.77734375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" style="5" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="31.2">
+    <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>24</v>
       </c>

--- a/xls/ab_tree.xlsx
+++ b/xls/ab_tree.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="264" yWindow="228" windowWidth="19200" windowHeight="7980" activeTab="7"/>
+    <workbookView xWindow="264" yWindow="228" windowWidth="19200" windowHeight="7980"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -23,26 +23,14 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
-    <t>stealing</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>stealth</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>lockpicking</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>barter</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>skinning</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>slash</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -128,6 +116,18 @@
   </si>
   <si>
     <t>intboost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>steal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lockpick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skin</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -516,15 +516,15 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F1" s="3"/>
     </row>
@@ -537,11 +537,11 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -564,11 +564,11 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="38.4" customHeight="1">
@@ -578,7 +578,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="B3" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -600,7 +600,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -637,10 +637,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="40.799999999999997" customHeight="1">
@@ -649,7 +649,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="B3" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="36" customHeight="1">
@@ -657,7 +657,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="B5" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -679,10 +679,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="40.200000000000003" customHeight="1">
@@ -692,7 +692,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="B3" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="36" customHeight="1">
@@ -700,7 +700,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="B5" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -722,10 +722,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="46.8" customHeight="1">
@@ -734,7 +734,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="B3" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -764,13 +764,13 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="43.2" customHeight="1">
@@ -783,7 +783,7 @@
     <row r="3" spans="1:5">
       <c r="B3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -813,13 +813,13 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:5">

--- a/xls/ab_tree.xlsx
+++ b/xls/ab_tree.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="264" yWindow="228" windowWidth="19200" windowHeight="7980"/>
+    <workbookView xWindow="270" yWindow="225" windowWidth="19200" windowHeight="7980"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -127,7 +127,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>skin</t>
+    <t>butcher</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -503,15 +503,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.88671875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.21875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="24.21875" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.25" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -528,7 +528,7 @@
       </c>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:6" ht="35.4" customHeight="1">
+    <row r="2" spans="1:6" ht="35.450000000000003" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -555,11 +555,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" customWidth="1"/>
-    <col min="3" max="3" width="20.5546875" customWidth="1"/>
+    <col min="1" max="1" width="10.75" customWidth="1"/>
+    <col min="2" max="2" width="13.125" customWidth="1"/>
+    <col min="3" max="3" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -571,7 +571,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="38.4" customHeight="1">
+    <row r="2" spans="1:3" ht="38.450000000000003" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -590,12 +590,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="12.109375" customWidth="1"/>
+    <col min="1" max="1" width="12.125" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="19.875" customWidth="1"/>
+    <col min="4" max="4" width="20.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -627,12 +627,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="11.88671875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11.875" style="5" customWidth="1"/>
     <col min="2" max="2" width="17" style="5" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" style="5" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="5"/>
+    <col min="3" max="3" width="18.375" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="8.875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -643,7 +643,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="40.799999999999997" customHeight="1">
+    <row r="2" spans="1:3" ht="40.9" customHeight="1">
       <c r="A2" s="4"/>
       <c r="C2" s="4"/>
     </row>
@@ -669,12 +669,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="15.77734375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" style="5" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="5"/>
+    <col min="1" max="1" width="12.625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="15.75" style="5" customWidth="1"/>
+    <col min="3" max="3" width="18.375" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="8.875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -685,7 +685,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="40.200000000000003" customHeight="1">
+    <row r="2" spans="1:3" ht="40.15" customHeight="1">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -712,12 +712,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" style="5" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="5"/>
+    <col min="1" max="1" width="16.5" style="5" customWidth="1"/>
+    <col min="2" max="2" width="18.125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="21.5" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="8.875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -728,7 +728,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="46.8" customHeight="1">
+    <row r="2" spans="1:3" ht="46.9" customHeight="1">
       <c r="A2" s="4"/>
       <c r="C2" s="4"/>
     </row>
@@ -752,14 +752,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="11.109375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11.5" style="5" customWidth="1"/>
+    <col min="2" max="2" width="9.5" style="5" customWidth="1"/>
+    <col min="3" max="3" width="8.75" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11.125" style="5" customWidth="1"/>
     <col min="5" max="5" width="13" style="5" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="5"/>
+    <col min="6" max="16384" width="8.875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -773,7 +773,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="43.2" customHeight="1">
+    <row r="2" spans="1:5" ht="43.15" customHeight="1">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -801,14 +801,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.21875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="8.88671875" style="5"/>
-    <col min="5" max="5" width="11.77734375" style="5" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="5"/>
+    <col min="1" max="1" width="11.75" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.25" style="5" customWidth="1"/>
+    <col min="3" max="3" width="13.75" style="5" customWidth="1"/>
+    <col min="4" max="4" width="8.875" style="5"/>
+    <col min="5" max="5" width="11.75" style="5" customWidth="1"/>
+    <col min="6" max="16384" width="8.875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">

--- a/xls/ab_tree.xlsx
+++ b/xls/ab_tree.xlsx
@@ -1,170 +1,155 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="270" yWindow="225" windowWidth="19200" windowHeight="7980"/>
   </bookViews>
   <sheets>
-    <sheet name="General" sheetId="1" r:id="rId1"/>
-    <sheet name="Sword" sheetId="2" r:id="rId2"/>
-    <sheet name="Archery" sheetId="3" r:id="rId3"/>
-    <sheet name="Fire" sheetId="4" r:id="rId4"/>
-    <sheet name="Ice" sheetId="5" r:id="rId5"/>
-    <sheet name="Poison" sheetId="6" r:id="rId6"/>
-    <sheet name="Support" sheetId="7" r:id="rId7"/>
-    <sheet name="Enhancement" sheetId="8" r:id="rId8"/>
+    <sheet sheetId="1" name="General" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Sword" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Archery" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Fire" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Ice" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Poison" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Support" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Enhancement" state="visible" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+  <si>
+    <t>steal</t>
+  </si>
+  <si>
+    <t>lockpick</t>
+  </si>
+  <si>
+    <t>butcher</t>
+  </si>
   <si>
     <t>stealth</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>barter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>slash</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thrust</t>
+  </si>
+  <si>
+    <t>swordmastery</t>
   </si>
   <si>
     <t>whirlwind</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>thrust</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swordmaster</t>
   </si>
   <si>
     <t>snipe</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>archeryexpert</t>
+  </si>
+  <si>
+    <t>archerymaster</t>
   </si>
   <si>
     <t>fireball</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>firewall</t>
   </si>
   <si>
     <t>combustion</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>meteorshower</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>firewall</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>icebolt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>icewall</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>deepfreeze</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>blizzard</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>poisondart</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poisonmist</t>
   </si>
   <si>
     <t>venomburst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>poisonmist</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>heal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>cure</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>holylight</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>purify</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>strboost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>agiboost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>intboost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>steal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lockpick</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>butcher</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="新細明體"/>
       <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <charset val="136"/>
+      <color theme="1"/>
+      <family val="1"/>
+      <scheme val="major"/>
+      <sz val="12"/>
       <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <charset val="136"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
-      <scheme val="major"/>
     </font>
     <font>
+      <charset val="136"/>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="微軟正黑體 Light"/>
-      <family val="2"/>
-      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -185,35 +170,39 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -501,96 +490,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="24.25" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.875" style="2"/>
+    <col min="1" max="1" width="11.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.25" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:6" ht="35.450000000000003" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1"/>
+    <row r="2" ht="35.45" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.75" customWidth="1"/>
     <col min="2" max="2" width="13.125" customWidth="1"/>
     <col min="3" max="3" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="38.450000000000003" customHeight="1">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="38.45" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -598,246 +591,244 @@
     <col min="4" max="4" width="20.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="17" style="5" customWidth="1"/>
-    <col min="3" max="3" width="18.375" style="5" customWidth="1"/>
-    <col min="4" max="16384" width="8.875" style="5"/>
+    <col min="1" max="1" width="11.875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="17" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.375" style="4" customWidth="1"/>
+    <col min="4" max="16384" width="8.875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="40.9" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="C2" s="4"/>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="B3" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="36" customHeight="1">
-      <c r="B4" s="4"/>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="B5" s="4" t="s">
-        <v>8</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" ht="40.9" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="5"/>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="15.75" style="5" customWidth="1"/>
-    <col min="3" max="3" width="18.375" style="5" customWidth="1"/>
-    <col min="4" max="16384" width="8.875" style="5"/>
+    <col min="1" max="1" width="12.625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="15.75" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.375" style="4" customWidth="1"/>
+    <col min="4" max="16384" width="8.875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="40.15" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="B3" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="36" customHeight="1">
-      <c r="B4" s="4"/>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="B5" s="4" t="s">
-        <v>13</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" ht="40.15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="5"/>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.5" style="5" customWidth="1"/>
-    <col min="2" max="2" width="18.125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="21.5" style="5" customWidth="1"/>
-    <col min="4" max="16384" width="8.875" style="5"/>
+    <col min="1" max="1" width="16.5" style="4" customWidth="1"/>
+    <col min="2" max="2" width="18.125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="21.5" style="4" customWidth="1"/>
+    <col min="4" max="16384" width="8.875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="46.9" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="C2" s="4"/>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="B3" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="B4" s="4"/>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="B5" s="4"/>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" ht="46.9" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="5"/>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.5" style="5" customWidth="1"/>
-    <col min="2" max="2" width="9.5" style="5" customWidth="1"/>
-    <col min="3" max="3" width="8.75" style="5" customWidth="1"/>
-    <col min="4" max="4" width="11.125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="13" style="5" customWidth="1"/>
-    <col min="6" max="16384" width="8.875" style="5"/>
+    <col min="1" max="1" width="11.5" style="4" customWidth="1"/>
+    <col min="2" max="2" width="9.5" style="4" customWidth="1"/>
+    <col min="3" max="3" width="8.75" style="4" customWidth="1"/>
+    <col min="4" max="4" width="11.125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="13" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="8.875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="43.15" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="B3" s="4"/>
-      <c r="D3" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="B4" s="4"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="B5" s="4"/>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" ht="43.15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="5"/>
+      <c r="D3" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="5"/>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.75" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.25" style="5" customWidth="1"/>
-    <col min="3" max="3" width="13.75" style="5" customWidth="1"/>
-    <col min="4" max="4" width="8.875" style="5"/>
-    <col min="5" max="5" width="11.75" style="5" customWidth="1"/>
-    <col min="6" max="16384" width="8.875" style="5"/>
+    <col min="1" max="1" width="11.75" style="4" customWidth="1"/>
+    <col min="2" max="2" width="11.25" style="4" customWidth="1"/>
+    <col min="3" max="3" width="13.75" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8.875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="11.75" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="8.875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="B3" s="4"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="B4" s="4"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="B5" s="4"/>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="5"/>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="5"/>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/xls/ab_tree.xlsx
+++ b/xls/ab_tree.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="225" windowWidth="19200" windowHeight="7980"/>
+    <workbookView xWindow="270" yWindow="225" windowWidth="19200" windowHeight="7980" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="General" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Sword" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Archery" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Fire" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Ice" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Poison" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Support" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Enhancement" state="visible" r:id="rId11"/>
+    <sheet name="General" sheetId="1" r:id="rId1"/>
+    <sheet name="Sword" sheetId="2" r:id="rId2"/>
+    <sheet name="Archery" sheetId="3" r:id="rId3"/>
+    <sheet name="Fire" sheetId="4" r:id="rId4"/>
+    <sheet name="Ice" sheetId="5" r:id="rId5"/>
+    <sheet name="Poison" sheetId="6" r:id="rId6"/>
+    <sheet name="Support" sheetId="7" r:id="rId7"/>
+    <sheet name="Enhancement" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>steal</t>
   </si>
@@ -68,6 +68,9 @@
     <t>firewall</t>
   </si>
   <si>
+    <t>fireballvolley</t>
+  </si>
+  <si>
     <t>combustion</t>
   </si>
   <si>
@@ -119,37 +122,44 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="5">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
       <charset val="136"/>
-      <color theme="1"/>
-      <family val="1"/>
       <scheme val="major"/>
-      <sz val="12"/>
-      <name val="新細明體"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <color theme="1"/>
-      <family val="2"/>
       <scheme val="minor"/>
-      <sz val="12"/>
-      <name val="新細明體"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體 Light"/>
+      <family val="2"/>
       <charset val="136"/>
-      <color theme="1"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="微軟正黑體 Light"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -191,7 +201,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -490,20 +500,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="24.25" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -517,14 +528,14 @@
       </c>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" ht="35.45" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="35.450000000000003" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -535,22 +546,23 @@
       <c r="D3" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.75" customWidth="1"/>
-    <col min="2" max="2" width="13.125" customWidth="1"/>
-    <col min="3" max="3" width="20.5" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -562,12 +574,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="38.45" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="38.450000000000003" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -576,22 +588,23 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.125" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="19.875" customWidth="1"/>
-    <col min="4" max="4" width="20.375" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -601,13 +614,13 @@
       </c>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="2"/>
       <c r="C3" s="1" t="s">
@@ -616,22 +629,24 @@
       <c r="D3" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" style="4" customWidth="1"/>
     <col min="2" max="2" width="17" style="4" customWidth="1"/>
-    <col min="3" max="3" width="18.375" style="4" customWidth="1"/>
-    <col min="4" max="16384" width="8.875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" style="4" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="5" t="s">
         <v>13</v>
       </c>
@@ -639,196 +654,215 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" ht="40.9" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="5"/>
       <c r="C2" s="5"/>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="5" t="s">
+    <row r="3" spans="1:3" ht="40.9" customHeight="1">
+      <c r="A3" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="5"/>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C3" s="5"/>
+    </row>
+    <row r="4" spans="1:3" ht="40.9" customHeight="1">
+      <c r="A4" s="5"/>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" spans="1:3">
       <c r="B5" s="5" t="s">
         <v>16</v>
       </c>
     </row>
+    <row r="6" spans="1:3" ht="36" customHeight="1">
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="15.75" style="4" customWidth="1"/>
-    <col min="3" max="3" width="18.375" style="4" customWidth="1"/>
-    <col min="4" max="16384" width="8.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" style="4" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" ht="40.15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="40.15" customHeight="1">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="B3" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36" customHeight="1">
       <c r="B4" s="5"/>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="B5" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.5" style="4" customWidth="1"/>
-    <col min="2" max="2" width="18.125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="21.5" style="4" customWidth="1"/>
-    <col min="4" max="16384" width="8.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" style="4" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" ht="46.9" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="46.9" customHeight="1">
       <c r="A2" s="5"/>
       <c r="C2" s="5"/>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="B3" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="B4" s="5"/>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="B5" s="5"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.5" style="4" customWidth="1"/>
-    <col min="2" max="2" width="9.5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="8.75" style="4" customWidth="1"/>
-    <col min="4" max="4" width="11.125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" style="4" customWidth="1"/>
     <col min="5" max="5" width="13" style="4" customWidth="1"/>
-    <col min="6" max="16384" width="8.875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" ht="43.15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="43.15" customHeight="1">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="B3" s="5"/>
       <c r="D3" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="B4" s="5"/>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="B5" s="5"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.75" style="4" customWidth="1"/>
-    <col min="2" max="2" width="11.25" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.75" style="4" customWidth="1"/>
-    <col min="4" max="4" width="8.875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="11.75" style="4" customWidth="1"/>
-    <col min="6" max="16384" width="8.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="B3" s="5"/>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="B4" s="5"/>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="B5" s="5"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>